--- a/项目1-汽车支腿反力/data/支腿反力验算.XLSX
+++ b/项目1-汽车支腿反力/data/支腿反力验算.XLSX
@@ -1719,7 +1719,7 @@
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="4">
-        <v>9.8</v>
+        <v>9.81</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>29</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F14" s="11">
         <f>(F6+F7+F8+F4)*F13</f>
-        <v>539.196</v>
+        <v>539.7462</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>33</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F15" s="11">
         <f>F9*F7*F13-F8*F13*F12+F4*F5*F13</f>
-        <v>981.96</v>
+        <v>982.962</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>37</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="F20" s="15">
         <f>F15*F18</f>
-        <v>631.844349434978</v>
+        <v>632.489088567055</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>37</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F21" s="15">
         <f>F15*F19</f>
-        <v>751.67689846575</v>
+        <v>752.443915709082</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>37</v>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F22" s="15">
         <f>F16*F14/2/F10-F20/2/F10+F21/2/F11</f>
-        <v>133.170696090578</v>
+        <v>133.306584555977</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>33</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="F23" s="15">
         <f>(F10-F16)*F14/2/F10+F20/2/F10+F21/2/F11</f>
-        <v>245.365984846487</v>
+        <v>245.616358300412</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>33</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F24" s="15">
         <f>F16*F14/2/F10-F20/2/F10-F21/2/F11</f>
-        <v>24.2320151535132</v>
+        <v>24.2567416995882</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>33</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F25" s="15">
         <f>(F10-F16)*F14/2/F10+F20/2/F10-F21/2/F11</f>
-        <v>136.427303909422</v>
+        <v>136.566515444023</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>33</v>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="F27" s="15">
         <f>F28/F26</f>
-        <v>61.3414962116217</v>
+        <v>61.404089575103</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>72</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F28" s="17">
         <f>MAX(F22:F25)</f>
-        <v>245.365984846487</v>
+        <v>245.616358300412</v>
       </c>
     </row>
   </sheetData>
